--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2024_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2024_antofagasta.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 15:02</t>
+    <t xml:space="preserve">2026-09-24 01:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -579,10 +579,10 @@
         <v>-0.2</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.19</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="3">
@@ -602,10 +602,10 @@
         <v>0.06</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.27</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="4">
@@ -625,10 +625,10 @@
         <v>-0.38</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="5">
@@ -648,10 +648,10 @@
         <v>0.26</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.07</v>
+        <v>0.1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="6">
@@ -671,10 +671,10 @@
         <v>0.54</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="7">
@@ -947,10 +947,10 @@
         <v>0.27</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.27</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="19">
@@ -970,10 +970,10 @@
         <v>-0.22</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="20">
@@ -993,10 +993,10 @@
         <v>-0.23</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="21">
@@ -1016,10 +1016,10 @@
         <v>-0.58</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.02</v>
+        <v>0.25</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="22">
@@ -1039,10 +1039,10 @@
         <v>-0.01</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.31</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.14</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="23">
@@ -1062,7 +1062,7 @@
         <v>0.03</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>-0.05</v>
@@ -1085,10 +1085,10 @@
         <v>-0.03</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.36</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="25">
@@ -1108,10 +1108,10 @@
         <v>-0.42</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.53</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="26">
@@ -1131,10 +1131,10 @@
         <v>0.02</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="27">
@@ -1154,10 +1154,10 @@
         <v>-0.29</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-0.62</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="28">
@@ -1177,10 +1177,10 @@
         <v>0.19</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="29">
@@ -1453,10 +1453,10 @@
         <v>-0.6</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-0.66</v>
+        <v>-0.67</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="41">
@@ -1476,10 +1476,10 @@
         <v>-0.08</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="42">
@@ -1499,10 +1499,10 @@
         <v>-0.1</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="43">
@@ -1522,10 +1522,10 @@
         <v>-0.14</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="44">
@@ -1545,10 +1545,10 @@
         <v>-0.37</v>
       </c>
       <c r="F44" s="2" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="G44" s="2" t="n">
         <v>-0.14</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>-0.23</v>
       </c>
     </row>
     <row r="45">
@@ -1571,7 +1571,7 @@
         <v>0.06</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="46">
@@ -2028,10 +2028,10 @@
         <v>0.19</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.43</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.36</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="66">
@@ -2051,10 +2051,10 @@
         <v>0.35</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="67">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2024_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2024_antofagasta.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:51</t>
+    <t xml:space="preserve">2026-10-01 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2024_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2024_antofagasta.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:06</t>
+    <t xml:space="preserve">2026-10-05 20:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
